--- a/forms/trg/Formulir_TRG_biomass.xlsx
+++ b/forms/trg/Formulir_TRG_biomass.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B31)</f>
+        <f>COUNTA(Anggota!B5:B32)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F31)</f>
+        <f>COUNTA(Anggota!F5:F32)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,22 +913,18 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Dr. Hikma Yanti, S.Hut., M.Si.</t>
+          <t>Prof. Syahidah, S.Hut., M.Si., Ph.D.</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Tanjungpura University</t>
-        </is>
-      </c>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Teknologi Hasil Hutan</t>
+          <t>Forest Product Chemistry</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -937,17 +933,17 @@
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-0334-7774</t>
+          <t>0000-0002-6506-7551</t>
         </is>
       </c>
       <c r="K5" s="11" t="inlineStr">
         <is>
-          <t>6706593</t>
+          <t>6005630</t>
         </is>
       </c>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>57208189748</t>
+          <t>57209641751</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -962,22 +958,22 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Fitriwati, SE., M.Si.</t>
+          <t>Dr. Hikma Yanti, S.Hut., M.Si.</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Tanjungpura University</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Microeconomics</t>
+          <t>Teknologi Hasil Hutan</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -986,17 +982,17 @@
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-0742-8339</t>
+          <t>0000-0003-0334-7774</t>
         </is>
       </c>
       <c r="K6" s="11" t="inlineStr">
         <is>
-          <t>6698582</t>
+          <t>6706593</t>
         </is>
       </c>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>59224077400</t>
+          <t>57208189748</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
@@ -1011,12 +1007,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Ira Taskirawati, S.Hut., M.Si., Ph.D.</t>
+          <t>Fitriwati, SE., M.Si.</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1026,7 +1022,7 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Mycology and Wood-destroying Insects</t>
+          <t>Microeconomics</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1035,17 +1031,17 @@
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-1467-4327</t>
+          <t>0000-0002-0742-8339</t>
         </is>
       </c>
       <c r="K7" s="11" t="inlineStr">
         <is>
-          <t>5997549</t>
+          <t>6698582</t>
         </is>
       </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>57209641644</t>
+          <t>59224077400</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -1060,12 +1056,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Dr. Kidung Tirtayasa Putra Pangestu, S.Hut., M.Si.</t>
+          <t>Ira Taskirawati, S.Hut., M.Si., Ph.D.</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1075,7 +1071,7 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Wood and Wood-Based Material Processing</t>
+          <t>Mycology and Wood-destroying Insects</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1084,17 +1080,17 @@
       <c r="I8" s="12" t="n"/>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-7341-8967</t>
+          <t>0000-0002-1467-4327</t>
         </is>
       </c>
       <c r="K8" s="11" t="inlineStr">
         <is>
-          <t>6789715</t>
+          <t>5997549</t>
         </is>
       </c>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>57209364109</t>
+          <t>57209641644</t>
         </is>
       </c>
       <c r="M8" s="11" t="inlineStr">
@@ -1109,12 +1105,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Astuti Arif, S.Hut., M.Si.</t>
+          <t>Dr. Kidung Tirtayasa Putra Pangestu, S.Hut., M.Si.</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1124,7 +1120,7 @@
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Wood Chemical and Biodeterioration</t>
+          <t>Wood and Wood-Based Material Processing</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1133,17 +1129,17 @@
       <c r="I9" s="12" t="n"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-3106-1642</t>
+          <t>0000-0001-7341-8967</t>
         </is>
       </c>
       <c r="K9" s="11" t="inlineStr">
         <is>
-          <t>5984139</t>
+          <t>6789715</t>
         </is>
       </c>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>57194242248</t>
+          <t>57209364109</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -1158,22 +1154,22 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Dr. Antonio Di Martino</t>
+          <t>Prof. Dr. Astuti Arif, S.Hut., M.Si.</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Tomsk Polytechnic University-Russia</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Materials Science, Biopolymers, Encapsulation</t>
+          <t>Wood Chemical and Biodeterioration</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1182,13 +1178,17 @@
       <c r="I10" s="12" t="n"/>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-2664-4483</t>
-        </is>
-      </c>
-      <c r="K10" s="12" t="n"/>
+          <t>0000-0003-3106-1642</t>
+        </is>
+      </c>
+      <c r="K10" s="11" t="inlineStr">
+        <is>
+          <t>5984139</t>
+        </is>
+      </c>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>55983525800</t>
+          <t>57194242248</t>
         </is>
       </c>
       <c r="M10" s="11" t="inlineStr">
@@ -1203,22 +1203,22 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Widya Fatriasari</t>
+          <t>Dr. Antonio Di Martino</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>National Research and Innovation Agency (BRIN)</t>
+          <t>Tomsk Polytechnic University-Russia</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Biomass Conversion, Lignin and Cellulose Valorization, Comprehensive Characterization of Natural Fiber</t>
+          <t>Materials Science, Biopolymers, Encapsulation</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -1227,17 +1227,13 @@
       <c r="I11" s="12" t="n"/>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-5166-9498</t>
-        </is>
-      </c>
-      <c r="K11" s="11" t="inlineStr">
-        <is>
-          <t>5998699</t>
-        </is>
-      </c>
+          <t>0000-0002-2664-4483</t>
+        </is>
+      </c>
+      <c r="K11" s="12" t="n"/>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>56690604600</t>
+          <t>55983525800</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
@@ -1252,22 +1248,22 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ummi Hani Abdullah</t>
+          <t>Prof. Dr. Widya Fatriasari</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Universiti Putra Malaysia</t>
+          <t>National Research and Innovation Agency (BRIN)</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Wood chemistry, Wood Composite, Adhesive and Coating, Wood Biomass, Polymers</t>
+          <t>Biomass Conversion, Lignin and Cellulose Valorization, Comprehensive Characterization of Natural Fiber</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -1276,13 +1272,17 @@
       <c r="I12" s="12" t="n"/>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-2021-1609</t>
-        </is>
-      </c>
-      <c r="K12" s="12" t="n"/>
+          <t>0000-0002-5166-9498</t>
+        </is>
+      </c>
+      <c r="K12" s="11" t="inlineStr">
+        <is>
+          <t>5998699</t>
+        </is>
+      </c>
       <c r="L12" s="11" t="inlineStr">
         <is>
-          <t>55315771800</t>
+          <t>56690604600</t>
         </is>
       </c>
       <c r="M12" s="11" t="inlineStr">
@@ -1297,22 +1297,22 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Assoc. Prof. ChM Dr. Fatimah Salim</t>
+          <t>Dr. Ummi Hani Abdullah</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>UiTM Shah Alam-Malaysia</t>
+          <t>Universiti Putra Malaysia</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Natural Product Chemistry, Ethnobotanical Plants, Organic Spectroscopy; Mass Spectrometry; Medicinal Chemistry</t>
+          <t>Wood chemistry, Wood Composite, Adhesive and Coating, Wood Biomass, Polymers</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
@@ -1321,13 +1321,13 @@
       <c r="I13" s="12" t="n"/>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-9560-068X</t>
+          <t>0000-0003-2021-1609</t>
         </is>
       </c>
       <c r="K13" s="12" t="n"/>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>55905027900</t>
+          <t>55315771800</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
@@ -1342,22 +1342,22 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Eka Novriyanti, S.Hut., M.Si., Ph.D.</t>
+          <t>Assoc. Prof. ChM Dr. Fatimah Salim</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>National Research and Innovation Agency</t>
+          <t>UiTM Shah Alam-Malaysia</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Plant Ecochemophysiology, Forest Product Technology, Plant Secondary Metabolite</t>
+          <t>Natural Product Chemistry, Ethnobotanical Plants, Organic Spectroscopy; Mass Spectrometry; Medicinal Chemistry</t>
         </is>
       </c>
       <c r="F14" s="12" t="n"/>
@@ -1366,17 +1366,13 @@
       <c r="I14" s="12" t="n"/>
       <c r="J14" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-9160-3274</t>
-        </is>
-      </c>
-      <c r="K14" s="11" t="inlineStr">
-        <is>
-          <t>6728196</t>
-        </is>
-      </c>
+          <t>0000-0001-9560-068X</t>
+        </is>
+      </c>
+      <c r="K14" s="12" t="n"/>
       <c r="L14" s="11" t="inlineStr">
         <is>
-          <t>http://www.scopus.com/inward/authorDetails.url?authorID=55212232700&amp;partnerID=MN8TOARS</t>
+          <t>55905027900</t>
         </is>
       </c>
       <c r="M14" s="11" t="inlineStr">
@@ -1391,27 +1387,43 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Fernando Da Silva</t>
+          <t>Eka Novriyanti, S.Hut., M.Si., Ph.D.</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
-      <c r="E15" s="11" t="n"/>
+          <t>National Research and Innovation Agency</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>Plant Ecochemophysiology, Forest Product Technology, Plant Secondary Metabolite</t>
+        </is>
+      </c>
       <c r="F15" s="12" t="n"/>
       <c r="G15" s="12" t="n"/>
       <c r="H15" s="12" t="n"/>
       <c r="I15" s="12" t="n"/>
-      <c r="J15" s="12" t="n"/>
-      <c r="K15" s="12" t="n"/>
-      <c r="L15" s="12" t="n"/>
+      <c r="J15" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-9160-3274</t>
+        </is>
+      </c>
+      <c r="K15" s="11" t="inlineStr">
+        <is>
+          <t>6728196</t>
+        </is>
+      </c>
+      <c r="L15" s="11" t="inlineStr">
+        <is>
+          <t>http://www.scopus.com/inward/authorDetails.url?authorID=55212232700&amp;partnerID=MN8TOARS</t>
+        </is>
+      </c>
       <c r="M15" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1424,12 +1436,12 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Syamsumarlin</t>
+          <t>Fernando Da Silva</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -1457,12 +1469,12 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Putri Endang Eka Lestari</t>
+          <t>Syamsumarlin</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -1490,12 +1502,12 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Siti Maimuna</t>
+          <t>Putri Endang Eka Lestari</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
@@ -1523,12 +1535,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Herawati</t>
+          <t>Siti Maimuna</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -1554,9 +1566,21 @@
       <c r="A20" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="12" t="n"/>
-      <c r="C20" s="12" t="n"/>
-      <c r="D20" s="12" t="n"/>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Herawati</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
       <c r="E20" s="11" t="n"/>
       <c r="F20" s="12" t="n"/>
       <c r="G20" s="12" t="n"/>
@@ -1565,7 +1589,11 @@
       <c r="J20" s="12" t="n"/>
       <c r="K20" s="12" t="n"/>
       <c r="L20" s="12" t="n"/>
-      <c r="M20" s="12" t="n"/>
+      <c r="M20" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -1754,15 +1782,32 @@
       <c r="L31" s="12" t="n"/>
       <c r="M31" s="12" t="n"/>
     </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="12" t="n"/>
+      <c r="C32" s="12" t="n"/>
+      <c r="D32" s="12" t="n"/>
+      <c r="E32" s="11" t="n"/>
+      <c r="F32" s="12" t="n"/>
+      <c r="G32" s="12" t="n"/>
+      <c r="H32" s="12" t="n"/>
+      <c r="I32" s="12" t="n"/>
+      <c r="J32" s="12" t="n"/>
+      <c r="K32" s="12" t="n"/>
+      <c r="L32" s="12" t="n"/>
+      <c r="M32" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
